--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194267</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194268</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194266</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194269</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194267</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194268</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194266</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194269</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194267</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194268</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194266</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194269</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194267</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194268</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194266</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194269</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194267</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194268</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131194266</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131194269</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194267</v>
+        <v>131194266</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>598738</v>
       </c>
       <c r="R2" t="n">
-        <v>6943066</v>
+        <v>6943074</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194268</v>
+        <v>131194267</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598698</v>
+        <v>598738</v>
       </c>
       <c r="R3" t="n">
-        <v>6943065</v>
+        <v>6943066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194266</v>
+        <v>131194268</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598738</v>
+        <v>598698</v>
       </c>
       <c r="R4" t="n">
-        <v>6943074</v>
+        <v>6943065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>131194269</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7704-2026 artfynd.xlsx
+++ b/artfynd/A 7704-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194266</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194267</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194268</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,8 +1172,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>